--- a/Budget Sheet.xlsx
+++ b/Budget Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35135D46-3D23-DC45-83A4-896ABC891C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D75EA1-9DD7-C34C-89F9-0CB8DAC16B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17380" activeTab="1" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="template" sheetId="3" r:id="rId1"/>
     <sheet name="May" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -439,7 +439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -458,46 +458,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,107 +992,107 @@
     </row>
     <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1"/>
     <row r="10" spans="2:19" ht="35" customHeight="1">
-      <c r="M10" s="14"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="15" t="s">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="P10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="35" customHeight="1">
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="O11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="3">
         <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
         <v>137</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="3">
         <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
         <v>137</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="6">
         <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
         <v>137</v>
       </c>
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="2:19" ht="35" customHeight="1">
-      <c r="M12" s="12"/>
-      <c r="N12" s="18" t="s">
+      <c r="M12" s="9"/>
+      <c r="N12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="3">
         <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
         <v>-137</v>
       </c>
-      <c r="P12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="7">
+      <c r="P12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3">
         <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="6">
         <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
         <v>0</v>
       </c>
       <c r="S12" s="3"/>
     </row>
     <row r="13" spans="2:19" ht="35" customHeight="1">
-      <c r="M13" s="12"/>
-      <c r="N13" s="18" t="s">
+      <c r="M13" s="9"/>
+      <c r="N13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="3">
         <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
         <v>-137</v>
       </c>
-      <c r="P13" s="7">
+      <c r="P13" s="3">
         <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R13" s="8">
+      <c r="Q13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="6">
         <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
         <v>0</v>
       </c>
       <c r="S13" s="3"/>
     </row>
     <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
-      <c r="M14" s="13"/>
-      <c r="N14" s="19" t="s">
+      <c r="M14" s="10"/>
+      <c r="N14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="7">
         <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
         <v>-137</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="7">
         <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="7">
         <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="S14" s="3"/>
@@ -1351,107 +1342,107 @@
     </row>
     <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1"/>
     <row r="10" spans="2:19" ht="35" customHeight="1">
-      <c r="M10" s="14"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="15" t="s">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="P10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="35" customHeight="1">
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="O11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="3">
         <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
         <v>134</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="3">
         <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
         <v>98</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="6">
         <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
         <v>1848</v>
       </c>
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="2:19" ht="35" customHeight="1">
-      <c r="M12" s="12"/>
-      <c r="N12" s="18" t="s">
+      <c r="M12" s="9"/>
+      <c r="N12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="3">
         <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
         <v>-134</v>
       </c>
-      <c r="P12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="7">
+      <c r="P12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
+        <v>-36</v>
+      </c>
+      <c r="R12" s="6">
+        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
+        <v>1714</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:19" ht="35" customHeight="1">
+      <c r="M13" s="9"/>
+      <c r="N13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="3">
+        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
+        <v>-98</v>
+      </c>
+      <c r="P13" s="3">
         <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
         <v>36</v>
       </c>
-      <c r="R12" s="8">
-        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
-        <v>1714</v>
-      </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="2:19" ht="35" customHeight="1">
-      <c r="M13" s="12"/>
-      <c r="N13" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="7">
-        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
-        <v>-98</v>
-      </c>
-      <c r="P13" s="7">
-        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
-        <v>-36</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R13" s="8">
+      <c r="Q13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="6">
         <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
         <v>1750</v>
       </c>
       <c r="S13" s="3"/>
     </row>
     <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
-      <c r="M14" s="13"/>
-      <c r="N14" s="19" t="s">
+      <c r="M14" s="10"/>
+      <c r="N14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="7">
         <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
         <v>-1848</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="7">
         <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
         <v>-1714</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="7">
         <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
         <v>-1750</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="S14" s="3"/>

--- a/Budget Sheet.xlsx
+++ b/Budget Sheet.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D75EA1-9DD7-C34C-89F9-0CB8DAC16B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D44773F-9A9C-2440-9048-BDF8A8834625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17380" activeTab="1" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="1" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
   </bookViews>
   <sheets>
-    <sheet name="template" sheetId="3" r:id="rId1"/>
-    <sheet name="May" sheetId="1" r:id="rId2"/>
+    <sheet name="May" sheetId="1" r:id="rId1"/>
+    <sheet name="June" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="30">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -252,6 +252,20 @@
     <t>from 松井</t>
     <rPh sb="5" eb="7">
       <t>マツイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイプC L字</t>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">ジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50V電圧計</t>
+    <rPh sb="3" eb="6">
+      <t>デンアテゥ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -824,286 +838,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB92768-9DEB-714E-838C-EFEA572EA42C}">
-  <dimension ref="B1:S14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="35" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1"/>
-    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.7109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:19" ht="20" customHeight="1"/>
-    <row r="2" spans="2:19" ht="35" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="3">
-        <f>SUM(C:C)</f>
-        <v>548</v>
-      </c>
-    </row>
-    <row r="3" spans="2:19" ht="35" customHeight="1">
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>548</v>
-      </c>
-      <c r="D3" s="1">
-        <f>ROUNDUP(C3/4,0)</f>
-        <v>137</v>
-      </c>
-      <c r="E3" s="2">
-        <v>46148</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19" ht="35" customHeight="1">
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="O4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="35" customHeight="1">
-      <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="M5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="3">
-        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3">
-        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="3"/>
-    </row>
-    <row r="6" spans="2:19" ht="35" customHeight="1">
-      <c r="D6" s="1"/>
-      <c r="E6" s="2"/>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="3">
-        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
-        <v>137</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="3">
-        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="3"/>
-    </row>
-    <row r="7" spans="2:19" ht="35" customHeight="1">
-      <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
-      <c r="N7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="3">
-        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
-        <v>137</v>
-      </c>
-      <c r="P7" s="3">
-        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" s="3">
-        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="3"/>
-    </row>
-    <row r="8" spans="2:19" ht="35" customHeight="1">
-      <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="N8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="3">
-        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
-        <v>137</v>
-      </c>
-      <c r="P8" s="3">
-        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1"/>
-    <row r="10" spans="2:19" ht="35" customHeight="1">
-      <c r="M10" s="11"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="35" customHeight="1">
-      <c r="M11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="3">
-        <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
-        <v>137</v>
-      </c>
-      <c r="Q11" s="3">
-        <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
-        <v>137</v>
-      </c>
-      <c r="R11" s="6">
-        <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
-        <v>137</v>
-      </c>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="2:19" ht="35" customHeight="1">
-      <c r="M12" s="9"/>
-      <c r="N12" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="3">
-        <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
-        <v>-137</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="3">
-        <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="2:19" ht="35" customHeight="1">
-      <c r="M13" s="9"/>
-      <c r="N13" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="3">
-        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
-        <v>-137</v>
-      </c>
-      <c r="P13" s="3">
-        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R13" s="6">
-        <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
-      <c r="M14" s="10"/>
-      <c r="N14" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="7">
-        <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
-        <v>-137</v>
-      </c>
-      <c r="P14" s="7">
-        <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="S14" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC956437-CEBA-2D43-9DC0-B2768359AD77}">
   <dimension ref="B1:S14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="35" customHeight="1"/>
@@ -1451,4 +1185,298 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A23EB8A-7596-1047-A85E-D5A29C4F82D8}">
+  <dimension ref="B1:S14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="35" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="20" customHeight="1"/>
+    <row r="2" spans="2:19" ht="35" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3">
+        <f>SUM(C:C)</f>
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" ht="35" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>598</v>
+      </c>
+      <c r="D3" s="1">
+        <f>ROUNDUP(C3/4,0)</f>
+        <v>150</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46192</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="35" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2167</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D8" si="0">ROUNDUP(C4/4,0)</f>
+        <v>542</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="35" customHeight="1">
+      <c r="D5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="M5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>542</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="2:19" ht="35" customHeight="1">
+      <c r="D6" s="1"/>
+      <c r="E6" s="2"/>
+      <c r="N6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>150</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="2:19" ht="35" customHeight="1">
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="N7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>150</v>
+      </c>
+      <c r="P7" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>542</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="2:19" ht="35" customHeight="1">
+      <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="N8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>150</v>
+      </c>
+      <c r="P8" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>542</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1"/>
+    <row r="10" spans="2:19" ht="35" customHeight="1">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="35" customHeight="1">
+      <c r="M11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="3">
+        <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
+        <v>392</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
+        <v>-150</v>
+      </c>
+      <c r="R11" s="6">
+        <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
+        <v>-150</v>
+      </c>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="2:19" ht="35" customHeight="1">
+      <c r="M12" s="9"/>
+      <c r="N12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="3">
+        <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
+        <v>-392</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
+        <v>-542</v>
+      </c>
+      <c r="R12" s="6">
+        <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
+        <v>-542</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:19" ht="35" customHeight="1">
+      <c r="M13" s="9"/>
+      <c r="N13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="3">
+        <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
+        <v>150</v>
+      </c>
+      <c r="P13" s="3">
+        <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
+        <v>542</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="6">
+        <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
+      <c r="M14" s="10"/>
+      <c r="N14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="7">
+        <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
+        <v>150</v>
+      </c>
+      <c r="P14" s="7">
+        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
+        <v>542</v>
+      </c>
+      <c r="Q14" s="7">
+        <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Budget Sheet.xlsx
+++ b/Budget Sheet.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D44773F-9A9C-2440-9048-BDF8A8834625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E51461-5217-D94A-9507-C40EC8EF03AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="1" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="2" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" r:id="rId1"/>
     <sheet name="June" sheetId="5" r:id="rId2"/>
+    <sheet name="July" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -266,6 +267,69 @@
     <t>50V電圧計</t>
     <rPh sb="3" eb="6">
       <t>デンアテゥ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JLCPCB①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋月電子通商①</t>
+    <rPh sb="0" eb="6">
+      <t>アキヅキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寺田</t>
+    <rPh sb="0" eb="1">
+      <t>テラダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UnitV 8個</t>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">コ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DRV8874 20個</t>
+    <rPh sb="10" eb="11">
+      <t xml:space="preserve">コ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50V電圧計 2個</t>
+    <rPh sb="3" eb="6">
+      <t>デンアテゥ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t xml:space="preserve">コ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USB C-Cケーブル 5本</t>
+    <rPh sb="13" eb="14">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USB C-Cケーブル 7本</t>
+    <rPh sb="13" eb="14">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>累積金額：</t>
+    <rPh sb="0" eb="4">
+      <t>ルイセキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -874,6 +938,12 @@
         <f>SUM(C:C)</f>
         <v>10506</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>10506</v>
+      </c>
     </row>
     <row r="3" spans="2:19" ht="35" customHeight="1">
       <c r="B3" s="1" t="s">
@@ -1224,6 +1294,13 @@
         <f>SUM(C:C)</f>
         <v>2765</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>10506+2765</f>
+        <v>13271</v>
+      </c>
     </row>
     <row r="3" spans="2:19" ht="35" customHeight="1">
       <c r="B3" s="1" t="s">
@@ -1251,7 +1328,7 @@
         <v>2167</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ref="D4:D8" si="0">ROUNDUP(C4/4,0)</f>
+        <f t="shared" ref="D4" si="0">ROUNDUP(C4/4,0)</f>
         <v>542</v>
       </c>
       <c r="E4" s="2">
@@ -1479,4 +1556,378 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4FCF3C-B521-6C40-BD2C-F6312369EC25}">
+  <dimension ref="B1:S14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="35" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="20" customHeight="1"/>
+    <row r="2" spans="2:19" ht="35" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3">
+        <f>SUM(C:C)</f>
+        <v>111511</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>10506+2765+111511</f>
+        <v>124782</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" ht="35" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3097</v>
+      </c>
+      <c r="D3" s="1">
+        <f>ROUNDUP(C3/4,0)</f>
+        <v>775</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="35" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1">
+        <v>36840</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D9" si="0">ROUNDUP(C4/4,0)</f>
+        <v>9210</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="35" customHeight="1">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1">
+        <v>58321</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>14581</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46212</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>138</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>26716</v>
+      </c>
+      <c r="R5" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>1027</v>
+      </c>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="2:19" ht="35" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>8598</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>2150</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46212</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>26716</v>
+      </c>
+      <c r="R6" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>1027</v>
+      </c>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="2:19" ht="35" customHeight="1">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>550</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>138</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>1027</v>
+      </c>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="2:19" ht="35" customHeight="1">
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3335</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>834</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>138</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>26716</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>770</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>193</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46233</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="35" customHeight="1">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="35" customHeight="1">
+      <c r="M11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="3">
+        <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
+        <v>138</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
+        <v>26716</v>
+      </c>
+      <c r="R11" s="6">
+        <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
+        <v>1027</v>
+      </c>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="2:19" ht="35" customHeight="1">
+      <c r="M12" s="9"/>
+      <c r="N12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="3">
+        <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
+        <v>-138</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
+        <v>26578</v>
+      </c>
+      <c r="R12" s="6">
+        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
+        <v>889</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:19" ht="35" customHeight="1">
+      <c r="M13" s="9"/>
+      <c r="N13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="3">
+        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
+        <v>-26716</v>
+      </c>
+      <c r="P13" s="3">
+        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
+        <v>-26578</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="6">
+        <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
+        <v>-25689</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
+      <c r="M14" s="10"/>
+      <c r="N14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="7">
+        <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
+        <v>-1027</v>
+      </c>
+      <c r="P14" s="7">
+        <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
+        <v>-889</v>
+      </c>
+      <c r="Q14" s="7">
+        <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
+        <v>25689</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Budget Sheet.xlsx
+++ b/Budget Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E51461-5217-D94A-9507-C40EC8EF03AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377FBC61-4FC8-0546-A84E-1C6D7F4ECFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="2" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
   </bookViews>
@@ -1593,14 +1593,14 @@
       </c>
       <c r="N2" s="3">
         <f>SUM(C:C)</f>
-        <v>111511</v>
+        <v>111630</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q2" s="3">
-        <f>10506+2765+111511</f>
-        <v>124782</v>
+        <f>10506+2765+111630</f>
+        <v>124901</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="35" customHeight="1">
@@ -1608,11 +1608,11 @@
         <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>3097</v>
+        <v>3216</v>
       </c>
       <c r="D3" s="1">
         <f>ROUNDUP(C3/4,0)</f>
-        <v>775</v>
+        <v>804</v>
       </c>
       <c r="E3" s="2">
         <v>46210</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Q5" s="3">
         <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>26716</v>
+        <v>26745</v>
       </c>
       <c r="R5" s="3">
         <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="Q6" s="3">
         <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>26716</v>
+        <v>26745</v>
       </c>
       <c r="R6" s="3">
         <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q8" s="3">
         <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
-        <v>26716</v>
+        <v>26745</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>19</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Q11" s="3">
         <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
-        <v>26716</v>
+        <v>26745</v>
       </c>
       <c r="R11" s="6">
         <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Q12" s="3">
         <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
-        <v>26578</v>
+        <v>26607</v>
       </c>
       <c r="R12" s="6">
         <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
@@ -1889,18 +1889,18 @@
       </c>
       <c r="O13" s="3">
         <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
-        <v>-26716</v>
+        <v>-26745</v>
       </c>
       <c r="P13" s="3">
         <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
-        <v>-26578</v>
+        <v>-26607</v>
       </c>
       <c r="Q13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="R13" s="6">
         <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
-        <v>-25689</v>
+        <v>-25718</v>
       </c>
       <c r="S13" s="3"/>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Q14" s="7">
         <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
-        <v>25689</v>
+        <v>25718</v>
       </c>
       <c r="R14" s="8" t="s">
         <v>19</v>

--- a/Budget Sheet.xlsx
+++ b/Budget Sheet.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377FBC61-4FC8-0546-A84E-1C6D7F4ECFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9305500B-EBE1-FF41-99D0-92A075788D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="2" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{D063ABBB-05E9-5048-A2E7-320821861EF2}"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" r:id="rId1"/>
     <sheet name="June" sheetId="5" r:id="rId2"/>
     <sheet name="July" sheetId="6" r:id="rId3"/>
+    <sheet name="August" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="42">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -330,6 +331,24 @@
     <t>累積金額：</t>
     <rPh sb="0" eb="4">
       <t>ルイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>半田付け用ボード</t>
+    <rPh sb="0" eb="3">
+      <t>ハンダヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JLCPCB②</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋月電子通商②</t>
+    <rPh sb="0" eb="6">
+      <t>アキヅキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1930,4 +1949,322 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8ED486-F60E-304C-B32D-E9A4FBEAEA4D}">
+  <dimension ref="B1:S14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="35" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="20" customHeight="1"/>
+    <row r="2" spans="2:19" ht="35" customHeight="1">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3">
+        <f>SUM(C:C)</f>
+        <v>29904</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>10506+2765+111630+29904</f>
+        <v>154805</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" ht="35" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>330</v>
+      </c>
+      <c r="D3" s="1">
+        <f>ROUNDUP(C3/4,0)</f>
+        <v>83</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="35" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>12485</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D9" si="0">ROUNDUP(C4/4,0)</f>
+        <v>3122</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46261</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="35" customHeight="1">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>17089</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>4273</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46261</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>7395</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>83</v>
+      </c>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="2:19" ht="35" customHeight="1">
+      <c r="D6" s="1"/>
+      <c r="E6" s="2"/>
+      <c r="N6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>83</v>
+      </c>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="2:19" ht="35" customHeight="1">
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="N7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>7395</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="3">
+        <f>SUMIF($B$3:$B$100,"松井",$D$3:$D$100)</f>
+        <v>83</v>
+      </c>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="2:19" ht="35" customHeight="1">
+      <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="N8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="3">
+        <f>SUMIF($B$3:$B$100,"明間",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <f>SUMIF($B$3:$B$100,"貝尻",$D$3:$D$100)</f>
+        <v>7395</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUMIF($B$3:$B$100,"寺田",$D$3:$D$100)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="2:19" ht="35" customHeight="1" thickBot="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:19" ht="35" customHeight="1">
+      <c r="M10" s="11"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="35" customHeight="1">
+      <c r="M11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="3">
+        <f>IF(P5&gt;O6,P5-O6,O6-P5)</f>
+        <v>7395</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>IF(Q5&gt;O7,Q5-O7,O7-Q5)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <f>IF(R5&gt;O8,R5-O8,O8-R5)</f>
+        <v>83</v>
+      </c>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="2:19" ht="35" customHeight="1">
+      <c r="M12" s="9"/>
+      <c r="N12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="3">
+        <f>IF(P5&lt;O6,P5-O6,O6-P5)</f>
+        <v>-7395</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>IF(Q6&lt;P7,Q6-P7,P7-Q6)</f>
+        <v>-7395</v>
+      </c>
+      <c r="R12" s="6">
+        <f>IF(R6&lt;P8,R6-P8,P8-R6)</f>
+        <v>-7312</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:19" ht="35" customHeight="1">
+      <c r="M13" s="9"/>
+      <c r="N13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="3">
+        <f>IF(Q5&lt;O7,Q5-O7,O7-Q5)</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <f>IF(Q6&gt;P7,Q6-P7,P7-Q6)</f>
+        <v>7395</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="6">
+        <f>IF(R7&gt;Q8,R7-Q8,Q8-R7)</f>
+        <v>83</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="2:19" ht="35" customHeight="1" thickBot="1">
+      <c r="M14" s="10"/>
+      <c r="N14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="7">
+        <f>IF(R5&lt;O8,R5-O8,O8-R5)</f>
+        <v>-83</v>
+      </c>
+      <c r="P14" s="7">
+        <f>IF(R6&gt;P8,R6-P8,P8-R6)</f>
+        <v>7312</v>
+      </c>
+      <c r="Q14" s="7">
+        <f>IF(R7&lt;Q8,R7-Q8,Q8-R7)</f>
+        <v>-83</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>